--- a/results/CB/CorrectionWithExistingValues.xlsx
+++ b/results/CB/CorrectionWithExistingValues.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Should be NULL ResponseType  - leave blank</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Should be NULL ResponseType  - leave blank</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Should be NULL ResponseType  - leave blank</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>, 9.35</t>
+          <t>GO, 9.35</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>, 8.95</t>
+          <t>GO, 8.95</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>, 9.09</t>
+          <t>GO, 9.09</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>, 9.13</t>
+          <t>GO, 9.13</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -10014,14 +10014,12 @@
           <t>NULL</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
+      <c r="G108" t="n">
+        <v>30</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -10046,7 +10044,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">, </t>
+          <t>NOGO, 30</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -10059,7 +10057,11 @@
           <t>ResponseTime</t>
         </is>
       </c>
-      <c r="P108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="Q108" t="inlineStr">
         <is>
           <t>NULL</t>
@@ -11473,7 +11475,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -11498,7 +11500,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>, 10.93</t>
+          <t>GO, 10.93</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -18849,7 +18851,7 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Should be NULL ResponseType  - leave blank</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
@@ -18936,7 +18938,7 @@
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Should be NULL ResponseType  - leave blank</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
@@ -19023,7 +19025,7 @@
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>Should be NULL ResponseType  - leave blank</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
@@ -24836,7 +24838,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -24861,7 +24863,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>, 9.35</t>
+          <t>GO, 9.35</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -24874,7 +24876,11 @@
           <t>ResponseType</t>
         </is>
       </c>
-      <c r="P271" t="inlineStr"/>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
       <c r="Q271" t="inlineStr">
         <is>
           <t>GO</t>
@@ -24887,7 +24893,7 @@
       </c>
       <c r="S271" t="inlineStr">
         <is>
-          <t>NOT EQUAL</t>
+          <t>EQUAL</t>
         </is>
       </c>
     </row>
@@ -24923,7 +24929,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -24948,7 +24954,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>, 8.95</t>
+          <t>GO, 8.95</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -24961,7 +24967,11 @@
           <t>ResponseType</t>
         </is>
       </c>
-      <c r="P272" t="inlineStr"/>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
       <c r="Q272" t="inlineStr">
         <is>
           <t>GO</t>
@@ -24974,7 +24984,7 @@
       </c>
       <c r="S272" t="inlineStr">
         <is>
-          <t>NOT EQUAL</t>
+          <t>EQUAL</t>
         </is>
       </c>
     </row>
@@ -27285,7 +27295,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -27310,7 +27320,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>, 9.09</t>
+          <t>GO, 9.09</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -27323,7 +27333,11 @@
           <t>ResponseType</t>
         </is>
       </c>
-      <c r="P298" t="inlineStr"/>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
       <c r="Q298" t="inlineStr">
         <is>
           <t>NOGO</t>
@@ -27372,7 +27386,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -27397,7 +27411,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>, 9.13</t>
+          <t>GO, 9.13</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -27410,7 +27424,11 @@
           <t>ResponseType</t>
         </is>
       </c>
-      <c r="P299" t="inlineStr"/>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
       <c r="Q299" t="inlineStr">
         <is>
           <t>NOGO</t>
@@ -27818,14 +27836,12 @@
           <t>NULL</t>
         </is>
       </c>
-      <c r="G304" t="inlineStr">
-        <is>
-          <t>NULL</t>
-        </is>
+      <c r="G304" t="n">
+        <v>30</v>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>NOGO</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -27850,7 +27866,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t xml:space="preserve">, </t>
+          <t>NOGO, 30</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -27863,7 +27879,11 @@
           <t>ResponseType</t>
         </is>
       </c>
-      <c r="P304" t="inlineStr"/>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>NOGO</t>
+        </is>
+      </c>
       <c r="Q304" t="inlineStr">
         <is>
           <t>NOGO</t>
@@ -27876,7 +27896,7 @@
       </c>
       <c r="S304" t="inlineStr">
         <is>
-          <t>NOT EQUAL</t>
+          <t>EQUAL</t>
         </is>
       </c>
     </row>
@@ -29277,7 +29297,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>NULL</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -29302,7 +29322,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>, 10.93</t>
+          <t>GO, 10.93</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -29315,7 +29335,11 @@
           <t>ResponseType</t>
         </is>
       </c>
-      <c r="P320" t="inlineStr"/>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
       <c r="Q320" t="inlineStr">
         <is>
           <t>NOGO</t>
